--- a/offline/variants_data/coldwar_redux/Cold_War_Redux.xlsx
+++ b/offline/variants_data/coldwar_redux/Cold_War_Redux.xlsx
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="G99" s="1" t="n">
         <v>28</v>
